--- a/2026年6月20日 初回開発/04 UAT/総合テストシナリオ.xlsx
+++ b/2026年6月20日 初回開発/04 UAT/総合テストシナリオ.xlsx
@@ -10,7 +10,7 @@
     <sheet name="テストシナリオ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'テストシナリオ'!$A$1:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'テストシナリオ'!$A$1:$I$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,12 +63,6 @@
         <bgColor rgb="00EFEFEF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -82,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,9 +91,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -467,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1558,27 +1549,27 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>[既知の調査中項目] Bluetoothシャッター機器の接続時に誤発火</t>
+          <t>Bluetoothシャッター機器の接続時に画面が初期化される</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>対局がすでに進行中の状態で、Bluetoothシャッター（音量キー代用型）を新たに接続する</t>
+          <t>対局がすでに進行中の状態で、Bluetoothシャッター（リモコン）を新たに接続する</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>①Bluetoothシャッターを接続する（操作はしない）</t>
+          <t>①Bluetoothシャッターのスイッチをオンにする（ボタン操作はしない）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>(あるべき動作)何も起きない / (現状報告されている問題)盤面が動いていないのに撮影が走り認識エラー→自動中止になる場合がある</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>調査中・対応保留</t>
+          <t>対局の進行状況を保ったまま何も起きない（以前はBT接続でAndroidのキーボード構成変化が起き、画面（Activity）が裏で再生成されて対局中の画面状態が初期化される不具合があったが、AndroidManifest.xmlにandroid:configChangesを宣言して再生成自体を止めた）</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1588,7 +1579,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5回目UAT課題①。発生したら音量キー検知トーストの有無・可能ならlogcatを記録して報告してほしい</t>
+          <t>6回目UAT課題①で根本解決。当初は音量キーの誤発火と誤診断していたが、実際はAndroidのActivity再生成が原因だった</t>
         </is>
       </c>
     </row>
@@ -2280,99 +2271,193 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>今後の検討（テスト対象外）</t>
+          <t>対局再開</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>KENTO連携（API直結）</t>
+          <t>中断局を盤面一致で再開</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>【対局中】（異常終了で残ったもの）または【対局中止】【対局エラー中止】のKIFが1局以上ある状態</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>①棋譜一覧でその対局を選び「対局再開」を押す ②キャリブレーション画面で「中断時点の棋譜通りに盤面を並べて撮影してください」の案内に従い、中断時点の盤面（持ち駒・手番は再現できないため見た目の駒位置のみ）を再現して撮影する ③盤面が一致</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>API連携は意図的に未対応（セキュリティ上の理由でユーザーが見送りを決定済み）。C-04のクリップボードコピーが正式な代替手段</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>対応見送り（確定）</t>
+          <t>グリッド確認画面→対局再開（game_idは変わらず、手数は中断時点から継続）。続けて撮影した手も正しく追記される</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>高</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>UAT指摘不要。仕様として確定済み</t>
+          <t>5回目UAT課題④で実装（commit 3a0904e）。本シナリオ作成時点で実機未検証</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
+          <t>対局再開</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>中断局を盤面不一致のまま「このまま進める」で再開</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>G-01と同じ前提</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>①②はG-01と同じ ③盤面を中断時点と少し違えて（駒を1つ間違えて）撮影する ④グリッド確認画面で不一致件数が表示され「このまま進める」を押す</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>認識結果（不一致を含む）を正として対局再開。手数・game_idは継続される</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>5回目UAT課題④の回答②（不一致時も新規対局と同じ選択UIを提供）に基づく。本シナリオ作成時点で実機未検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>対局再開</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>中断局を盤面不一致から手動タップで直して再開</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>G-01と同じ前提</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>①②③はG-02と同じ ④「手動タップで直す」を押し、同じ写真のまま盤の四隅をタップする</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>手動タップ結果（無条件採用）を正として対局再開</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>本シナリオ作成時点で実機未検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>今後の検討（テスト対象外）</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>対局再開機能（中断局からの再開）</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>KENTO連携（API直結）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>5回目UAT課題④で実現性検討中。現時点では未実装のため、対局中止後に途中から再開することはできない</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>未実装・検討中</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>API連携は意図的に未対応（セキュリティ上の理由でユーザーが見送りを決定済み）。C-04のクリップボードコピーが正式な代替手段</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>対応見送り（確定）</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>UAT指摘不要。実装後にあらためてシナリオ追加予定</t>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>UAT指摘不要。仕様として確定済み</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I42"/>
+  <autoFilter ref="A1:I44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2026年6月20日 初回開発/04 UAT/総合テストシナリオ.xlsx
+++ b/2026年6月20日 初回開発/04 UAT/総合テストシナリオ.xlsx
@@ -10,7 +10,7 @@
     <sheet name="テストシナリオ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'テストシナリオ'!$A$1:$I$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'テストシナリオ'!$A$1:$I$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1895,32 +1895,32 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>D-01</t>
+          <t>C-08</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>KIFファイル管理</t>
+          <t>棋譜一覧・共有（Web）</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>対局中のファイル名形式</t>
+          <t>ブラウザから棋譜一覧を表示</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>対局を開始した直後</t>
+          <t>サーバー（uvicorn）が起動している状態</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>①サーバーの保存先（00 runtime/server/runtime/games）を確認する</t>
+          <t>①PCまたはスマホのブラウザで http://&lt;サーバーIP&gt;:8000/web を開く</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>【対局中】yyyyMMdd_hh-mm.kif の形式で作成されている</t>
+          <t>/web/games にリダイレクトされ、保存済みの対局が一覧表示される（Androidアプリと同じGET /gamesを利用）</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -1930,44 +1930,44 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>開発者向け確認項目</t>
+          <t>追加要望（2026-06-23）。テンプレートエンジン等の新規依存なし、薄いHTML/JS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>D-02</t>
+          <t>C-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>KIFファイル管理</t>
+          <t>棋譜一覧・共有（Web）</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>終局時のファイル名変化</t>
+          <t>ブラウザから日付で絞り込み</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>B-08/B-09で終局した直後</t>
+          <t>C-08の一覧画面にいる状態</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>①保存先を確認する</t>
+          <t>①日付入力欄で日付を選ぶ</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>ファイル名の【対局中】が【対局完了】に変わっている</t>
+          <t>その日付のKIFだけに絞り込まれる</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -1980,41 +1980,37 @@
           <t>低</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>開発者向け確認項目</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>D-03</t>
+          <t>C-10</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>KIFファイル管理</t>
+          <t>棋譜一覧・共有（Web）</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>中止時のファイル名変化</t>
+          <t>ブラウザからKIF詳細表示・共有・コピー</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>B-10で中止した直後</t>
+          <t>C-08の一覧画面にいる状態</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>①保存先を確認する</t>
+          <t>①対局を1つクリック ②「共有」または「コピー（分析Tool貼付用）」ボタンを押す</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>ファイル名の【対局中】が【対局中止】に変わっている</t>
+          <t>KIF本文が表示される。「共有」は対応ブラウザ（Android Chrome等）ならOSの共有シートが開き、未対応ならクリップボードにコピーされる。「コピー」は常にクリップボードにコピーされる</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2024,44 +2020,44 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>開発者向け確認項目</t>
+          <t>LAN内の平文HTTP運用のため、navigator.clipboardが使えない場合はdocument.execCommand('copy')にフォールバックする実装。本シナリオ作成時点で実際のブラウザでの動作は未検証</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>D-04</t>
+          <t>C-11</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>KIFファイル管理</t>
+          <t>棋譜一覧・共有（Web）</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>自動中止（エラー）時のファイル名変化</t>
+          <t>ブラウザ版に「対局再開」ボタンがないことの確認</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>B-03/B-05で自動中止した直後</t>
+          <t>C-08〜C-10のいずれかの画面にいる状態</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>①保存先を確認する</t>
+          <t>①画面を確認する</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>ファイル名の【対局中】が【対局エラー中止】に変わっている</t>
+          <t>「対局再開」に相当するボタン・リンクは表示されない（要望により意図的に未実装）</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2076,14 +2072,14 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>開発者向け確認項目</t>
+          <t>PC等のブラウザから中断局を再開する運用は想定していないため</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>D-05</t>
+          <t>D-01</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2093,69 +2089,69 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>KIFの時間記録</t>
+          <t>対局中のファイル名形式</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>対局を開始し、何手か進めた状態</t>
+          <t>対局を開始した直後</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>①KIFファイルを開いて確認する</t>
+          <t>①サーバーの保存先（00 runtime/server/runtime/games）を確認する</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>対局開始時刻（キャリブレーション完了→対局画面遷移時）と、各手のだいたいの経過時間が記録されている</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>5回目UAT②対応中</t>
+          <t>【対局中】yyyyMMdd_hh-mm.kif の形式で作成されている</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>厳密な時間でなくおおよそでよい、という要件。本シナリオ作成時点では未実装〜対応中</t>
+          <t>開発者向け確認項目</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>E-01</t>
+          <t>D-02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>サーバー・環境</t>
+          <t>KIFファイル管理</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>再起動直後の初回撮影の速度</t>
+          <t>終局時のファイル名変化</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>サーバー（uvicorn）を起動した直後</t>
+          <t>B-08/B-09で終局した直後</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>①起動直後にキャリブレーション撮影を行う</t>
+          <t>①保存先を確認する</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>異常に遅くならない（起動時ウォームアップ済みのため、通常と同程度の応答時間になる）</t>
+          <t>ファイル名の【対局中】が【対局完了】に変わっている</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2165,44 +2161,44 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>過去に初回のみ約17秒かかる不具合があり、起動時ウォームアップで解消済み</t>
+          <t>開発者向け確認項目</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>E-02</t>
+          <t>D-03</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>サーバー・環境</t>
+          <t>KIFファイル管理</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>サーバーIPアドレスの安定性</t>
+          <t>中止時のファイル名変化</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PCを再起動した後など</t>
+          <t>B-10で中止した直後</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>①アプリからサーバーに接続する</t>
+          <t>①保存先を確認する</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>192.168.0.24（DHCP予約済み）に変わらず接続できる</t>
+          <t>ファイル名の【対局中】が【対局中止】に変わっている</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -2212,44 +2208,44 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5回目UAT⑤で対応。IPが変わった場合は要再確認</t>
+          <t>開発者向け確認項目</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>E-03</t>
+          <t>D-04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>サーバー・環境</t>
+          <t>KIFファイル管理</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>サーバーの起動場所</t>
+          <t>自動中止（エラー）時のファイル名変化</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>サーバーを起動するとき</t>
+          <t>B-03/B-05で自動中止した直後</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>①「00 runtime/サーバー起動コマンド.txt」記載の手順で起動する</t>
+          <t>①保存先を確認する</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>00 runtime/server/ 配下から正常に起動する（旧フォルダからは起動しない運用に変更済み）</t>
+          <t>ファイル名の【対局中】が【対局エラー中止】に変わっている</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -2264,86 +2260,86 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5回目UAT③対応。開発者向け確認項目</t>
+          <t>開発者向け確認項目</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>D-05</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>対局再開</t>
+          <t>KIFファイル管理</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>中断局を盤面一致で再開</t>
+          <t>KIFの時間記録</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>【対局中】（異常終了で残ったもの）または【対局中止】【対局エラー中止】のKIFが1局以上ある状態</t>
+          <t>対局を開始し、何手か進めた状態</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>①棋譜一覧でその対局を選び「対局再開」を押す ②キャリブレーション画面で「中断時点の棋譜通りに盤面を並べて撮影してください」の案内に従い、中断時点の盤面（持ち駒・手番は再現できないため見た目の駒位置のみ）を再現して撮影する ③盤面が一致</t>
+          <t>①KIFファイルを開いて確認する</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>グリッド確認画面→対局再開（game_idは変わらず、手数は中断時点から継続）。続けて撮影した手も正しく追記される</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>実装済み</t>
+          <t>対局開始時刻（キャリブレーション完了→対局画面遷移時）と、各手のだいたいの経過時間が記録されている</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>5回目UAT②対応中</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5回目UAT課題④で実装（commit 3a0904e）。本シナリオ作成時点で実機未検証</t>
+          <t>厳密な時間でなくおおよそでよい、という要件。本シナリオ作成時点では未実装〜対応中</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>E-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>対局再開</t>
+          <t>サーバー・環境</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>中断局を盤面不一致のまま「このまま進める」で再開</t>
+          <t>再起動直後の初回撮影の速度</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>G-01と同じ前提</t>
+          <t>サーバー（uvicorn）を起動した直後</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>①②はG-01と同じ ③盤面を中断時点と少し違えて（駒を1つ間違えて）撮影する ④グリッド確認画面で不一致件数が表示され「このまま進める」を押す</t>
+          <t>①起動直後にキャリブレーション撮影を行う</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>認識結果（不一致を含む）を正として対局再開。手数・game_idは継続される</t>
+          <t>異常に遅くならない（起動時ウォームアップ済みのため、通常と同程度の応答時間になる）</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -2358,39 +2354,39 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5回目UAT課題④の回答②（不一致時も新規対局と同じ選択UIを提供）に基づく。本シナリオ作成時点で実機未検証</t>
+          <t>過去に初回のみ約17秒かかる不具合があり、起動時ウォームアップで解消済み</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>G-03</t>
+          <t>E-02</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>対局再開</t>
+          <t>サーバー・環境</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>中断局を盤面不一致から手動タップで直して再開</t>
+          <t>サーバーIPアドレスの安定性</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>G-01と同じ前提</t>
+          <t>PCを再起動した後など</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>①②③はG-02と同じ ④「手動タップで直す」を押し、同じ写真のまま盤の四隅をタップする</t>
+          <t>①アプリからサーバーに接続する</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>手動タップ結果（無条件採用）を正として対局再開</t>
+          <t>192.168.0.24（DHCP予約済み）に変わらず接続できる</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -2405,59 +2401,247 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>本シナリオ作成時点で実機未検証</t>
+          <t>5回目UAT⑤で対応。IPが変わった場合は要再確認</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>E-03</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>サーバー・環境</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>サーバーの起動場所</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>サーバーを起動するとき</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>①「00 runtime/サーバー起動コマンド.txt」記載の手順で起動する</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>00 runtime/server/ 配下から正常に起動する（旧フォルダからは起動しない運用に変更済み）</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>5回目UAT③対応。開発者向け確認項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>対局再開</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>中断局を盤面一致で再開</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>【対局中】（異常終了で残ったもの）または【対局中止】【対局エラー中止】のKIFが1局以上ある状態</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>①棋譜一覧でその対局を選び「対局再開」を押す ②キャリブレーション画面で「中断時点の棋譜通りに盤面を並べて撮影してください」の案内に従い、中断時点の盤面（持ち駒・手番は再現できないため見た目の駒位置のみ）を再現して撮影する ③盤面が一致</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>グリッド確認画面→対局再開（game_idは変わらず、手数は中断時点から継続）。続けて撮影した手も正しく追記される</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>5回目UAT課題④で実装（commit 3a0904e）。本シナリオ作成時点で実機未検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>対局再開</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>中断局を盤面不一致のまま「このまま進める」で再開</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>G-01と同じ前提</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>①②はG-01と同じ ③盤面を中断時点と少し違えて（駒を1つ間違えて）撮影する ④グリッド確認画面で不一致件数が表示され「このまま進める」を押す</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>認識結果（不一致を含む）を正として対局再開。手数・game_idは継続される</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>5回目UAT課題④の回答②（不一致時も新規対局と同じ選択UIを提供）に基づく。本シナリオ作成時点で実機未検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>対局再開</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>中断局を盤面不一致から手動タップで直して再開</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>G-01と同じ前提</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>①②③はG-02と同じ ④「手動タップで直す」を押し、同じ写真のまま盤の四隅をタップする</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>手動タップ結果（無条件採用）を正として対局再開</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>本シナリオ作成時点で実機未検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>F-01</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>今後の検討（テスト対象外）</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>KENTO連携（API直結）</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>API連携は意図的に未対応（セキュリティ上の理由でユーザーが見送りを決定済み）。C-04のクリップボードコピーが正式な代替手段</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>対応見送り（確定）</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>UAT指摘不要。仕様として確定済み</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I44"/>
+  <autoFilter ref="A1:I48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>